--- a/ARRIVE_Backend.xlsx
+++ b/ARRIVE_Backend.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الحالات المتأخرة" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإعدادات" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Sequence" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الموظفون" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_AuditLog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,6 +475,7 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,10 +591,15 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>معرّف الفرع (داخلي)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>آخر تعديل</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>المستخدم المعدّل</t>
         </is>
@@ -602,13 +610,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -623,133 +631,67 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رقم السجل</t>
+          <t>Employee ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>تاريخ الإدخال</t>
+          <t>الاسم الكامل</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>وقت الإدخال</t>
+          <t>اسم المستخدم</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>المستخدم (مُدخل السجل)</t>
+          <t>Password Hash</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>التاريخ</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>الفرع</t>
+          <t>الدور</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>رقم البوليصة</t>
+          <t>الفروع المسموحة</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>المرسل / التاجر</t>
+          <t>الحالة</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>العميل</t>
+          <t>تاريخ الإنشاء</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>سبب المرتجع</t>
+          <t>آخر تسجيل دخول</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>تاريخ تسجيل المرتجع</t>
+          <t>محاولات الدخول الفاشلة</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>تاريخ وصول المرتجع</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>حالة المطابقة</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>نتيجة المراجعة</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>حالة الشحنة بالنظام</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>الحالة الفعلية</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>سبب عدم المطابقة</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>مسؤول المتابعة</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>حالة الإغلاق</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الإغلاق</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>آخر تعديل</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>المستخدم المعدّل</t>
+          <t>آخر محاولة فاشلة</t>
         </is>
       </c>
     </row>
@@ -758,7 +700,55 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>التاريخ والوقت</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>العملية</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النتيجة</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>التفاصيل</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -821,6 +811,169 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>الفرع</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>رقم البوليصة</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>المرسل / التاجر</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>العميل</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>سبب المرتجع</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ تسجيل المرتجع</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ وصول المرتجع</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>حالة المطابقة</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>نتيجة المراجعة</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>حالة الشحنة بالنظام</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>الحالة الفعلية</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>سبب عدم المطابقة</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>مسؤول المتابعة</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>حالة الإغلاق</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ الإغلاق</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>معرّف الفرع (داخلي)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>آخر تعديل</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم المعدّل</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم السجل</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ الإدخال</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>وقت الإدخال</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم (مُدخل السجل)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>وقت العملية</t>
         </is>
       </c>
@@ -906,10 +1059,15 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>معرّف الفرع (داخلي)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>آخر تعديل</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>المستخدم المعدّل</t>
         </is>
@@ -921,6 +1079,558 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم السجل</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ الإدخال</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>وقت الإدخال</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم (مُدخل السجل)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ التحويل</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>رقم التحويل</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>رقم البوليصة</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>الفرع المحول</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>الفرع المستلم</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>مسؤول التحويل</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ ووقت الإرسال</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ ووقت الاستلام</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>حالة التحويل</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>هل تم التأكيد؟</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>وسيلة التأكيد</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>وقت التأكيد</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>وجود مشكلة</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>نوع المشكلة</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>المسؤول عن المتابعة</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>حالة الإغلاق</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>مدة الوصول (ساعة)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>مدة تأكيد التحويل (ساعة)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>حالة الالتزام الزمني بالتأكيد (محسوبة)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>معرّف الفرع المحول (داخلي)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>معرّف الفرع المستلم (داخلي)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>آخر تعديل</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم المعدّل</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم السجل</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ الإدخال</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>وقت الإدخال</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم (مُدخل السجل)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ الاكتشاف</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>وقت الاكتشاف</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الفرع</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>مصدر اكتشاف المشكلة</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>نوع المشكلة</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>وصف المشكلة</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>رقم البوليصة إن وجد</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>عدد الحالات المتأثرة</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>درجة الأولوية</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>المسؤول عن الحل</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>الإجراء المطلوب</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ الاستحقاق</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>حالة المشكلة</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ الإغلاق</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>سبب التأخير</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>الإجراء الوقائي</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ملاحظات المدقق</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>مدة الإغلاق (أيام)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>تنبيه التأخر</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>تصنيف الإغلاق (محسوب)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>معرّف الفرع (داخلي)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>آخر تعديل</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم المعدّل</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم السجل</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ الإدخال</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>وقت الإدخال</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم (مُدخل السجل)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ تسجيل المخالفة</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ اعتماد الجزاء</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الفرع</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الموظف</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>الرقم الوظيفي إن وجد</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>نوع المخالفة</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>وصف المخالفة</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>مرجع المشكلة أو البوليصة</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>درجة المخالفة</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>هل تمت المراجعة؟</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>قرار المراجعة</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>نوع الجزاء المعتمد</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>قيمة الجزاء</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>جهة الاعتماد</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>حالة الجزاء</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>تاريخ التنفيذ</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>حالة التظلم إن وجد</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>القيمة المعتمدة (محسوبة)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>القيمة المنفذة فعليًا (محسوبة)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>معرّف الفرع (داخلي)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>آخر تعديل</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>المستخدم المعدّل</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -980,102 +1690,102 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>تاريخ التحويل</t>
+          <t>تاريخ الرصد</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>رقم التحويل</t>
+          <t>رقم البوليصة</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>رقم البوليصة</t>
+          <t>الفرع</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>الفرع المحول</t>
+          <t>المحافظة / المنطقة</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>الفرع المستلم</t>
+          <t>المرسل</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>مسؤول التحويل</t>
+          <t>حالة الشحنة</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>تاريخ ووقت الإرسال</t>
+          <t>تاريخ إنشاء الطلب</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>تاريخ ووقت الاستلام</t>
+          <t>سبب التأخير</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>حالة التحويل</t>
+          <t>المسؤول عن المتابعة</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>هل تم التأكيد؟</t>
+          <t>الإجراء المطلوب</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>وسيلة التأكيد</t>
+          <t>حالة الإجراء</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>وقت التأكيد</t>
+          <t>تاريخ الإغلاق</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>وجود مشكلة</t>
+          <t>ملاحظات</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>نوع المشكلة</t>
+          <t>عمر الطلب بالأيام (من تاريخ إنشاء الطلب)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>المسؤول عن المتابعة</t>
+          <t>عمر الحالة بالأيام (من تاريخ الرصد)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>حالة الإغلاق</t>
+          <t>مدة عدم التحديث بالأيام</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>ملاحظات</t>
+          <t>الحد المستهدف (من الإعدادات)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>مدة الوصول (ساعة)</t>
+          <t>عدد أيام التجاوز بعد الاستحقاق</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>مدة تأكيد التحويل (ساعة)</t>
+          <t>تصنيف التأخير</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>حالة الالتزام الزمني بالتأكيد (محسوبة)</t>
+          <t>معرّف الفرع (داخلي)</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
@@ -1084,532 +1794,6 @@
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>المستخدم المعدّل</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AB1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>رقم السجل</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الإدخال</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>وقت الإدخال</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>المستخدم (مُدخل السجل)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الاكتشاف</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>وقت الاكتشاف</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>الفرع</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>القسم</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>مصدر اكتشاف المشكلة</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>نوع المشكلة</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>وصف المشكلة</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>رقم البوليصة إن وجد</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>عدد الحالات المتأثرة</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>درجة الأولوية</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>المسؤول عن الحل</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>الإجراء المطلوب</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الاستحقاق</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>حالة المشكلة</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الإغلاق</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>سبب التأخير</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>الإجراء الوقائي</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>ملاحظات المدقق</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>مدة الإغلاق (أيام)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>تنبيه التأخر</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>تصنيف الإغلاق (محسوب)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>آخر تعديل</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>المستخدم المعدّل</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>رقم السجل</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الإدخال</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>وقت الإدخال</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>المستخدم (مُدخل السجل)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ تسجيل المخالفة</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ اعتماد الجزاء</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>الفرع</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>اسم الموظف</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>الرقم الوظيفي إن وجد</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>نوع المخالفة</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>وصف المخالفة</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>مرجع المشكلة أو البوليصة</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>درجة المخالفة</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>هل تمت المراجعة؟</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>قرار المراجعة</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>نوع الجزاء المعتمد</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>قيمة الجزاء</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>جهة الاعتماد</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>حالة الجزاء</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ التنفيذ</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>حالة التظلم إن وجد</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>القيمة المعتمدة (محسوبة)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>القيمة المنفذة فعليًا (محسوبة)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>آخر تعديل</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>المستخدم المعدّل</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Y1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>رقم السجل</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الإدخال</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>وقت الإدخال</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>المستخدم (مُدخل السجل)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الرصد</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>رقم البوليصة</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>الفرع</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>المحافظة / المنطقة</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>المرسل</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>حالة الشحنة</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ إنشاء الطلب</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>سبب التأخير</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>المسؤول عن المتابعة</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>الإجراء المطلوب</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>حالة الإجراء</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>تاريخ الإغلاق</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>عمر الطلب بالأيام (من تاريخ إنشاء الطلب)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>عمر الحالة بالأيام (من تاريخ الرصد)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>مدة عدم التحديث بالأيام</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>الحد المستهدف (من الإعدادات)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>عدد أيام التجاوز بعد الاستحقاق</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>تصنيف التأخير</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>آخر تعديل</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>المستخدم المعدّل</t>
         </is>
@@ -1626,7 +1810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1640,6 +1824,16 @@
           <t>القيمة</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>المعرّف (للفروع فقط)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>الحالة (للفروع فقط)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1652,6 +1846,16 @@
           <t>القاهرة الجديدة</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1664,6 +1868,16 @@
           <t>مدينة نصر</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BR-002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1676,6 +1890,16 @@
           <t>المعادي</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BR-003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1688,6 +1912,16 @@
           <t>6 أكتوبر</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BR-004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1700,6 +1934,16 @@
           <t>الشيخ زايد</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BR-005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1712,6 +1956,16 @@
           <t>الإسكندرية - سموحة</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1724,6 +1978,16 @@
           <t>الإسكندرية - محرم بك</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BR-007</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1736,6 +2000,16 @@
           <t>المنصورة</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BR-008</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1748,6 +2022,16 @@
           <t>طنطا</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BR-009</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1760,6 +2044,16 @@
           <t>الزقازيق</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BR-010</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1772,6 +2066,16 @@
           <t>أسيوط</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BR-011</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1784,6 +2088,16 @@
           <t>المنيا</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BR-012</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1796,6 +2110,16 @@
           <t>بني سويف</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BR-013</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1808,6 +2132,16 @@
           <t>الفيوم</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BR-014</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1820,6 +2154,16 @@
           <t>دمياط</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BR-015</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2682,90 +3026,100 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>auth_enabled</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>فئات عمر الحالات المتأخرة</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>من</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>إلى</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>التصنيف</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>0</v>
-      </c>
-      <c r="B96" t="n">
-        <v>5</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>0–5 أيام</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>6–10 أيام</t>
+          <t>0–5 أيام</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>11–15 يومًا</t>
+          <t>6–10 أيام</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B99" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>16–20 يومًا</t>
+          <t>11–15 يومًا</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
+        <v>16</v>
+      </c>
+      <c r="B100" t="n">
+        <v>20</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>16–20 يومًا</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
         <v>21</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B101" t="n">
         <v>99999</v>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>أكثر من 20 يومًا</t>
         </is>
